--- a/Assets/Excel/RewardData.xlsx
+++ b/Assets/Excel/RewardData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14775" windowHeight="8205"/>
+    <workbookView windowWidth="14190" windowHeight="10845"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <t>Jmz</t>
   </si>
   <si>
-    <t>Yq</t>
+    <t>Tq</t>
   </si>
   <si>
     <t>Jyb</t>
@@ -52,7 +52,7 @@
     <t>金芒珠数值</t>
   </si>
   <si>
-    <t>银钱</t>
+    <t>铜钱</t>
   </si>
   <si>
     <t>金元宝</t>
